--- a/data/raw/products.xlsx
+++ b/data/raw/products.xlsx
@@ -1,3 +1,141 @@
+
+<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
+  <sheets>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="US" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EU" sheetId="2" state="visible" r:id="rId2"/>
+  </sheets>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+</workbook>
+</file>
+
+<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
+  </fonts>
+  <fills count="2">
+    <fill>
+      <patternFill/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+  </fills>
+  <borders count="2">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+  </borders>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+  </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  </cellStyles>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
+</styleSheet>
+</file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
@@ -280,4 +418,2896 @@
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
 </a:theme>
+</file>
+
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>product_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>unit_price</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>stock_quantity</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>supplier</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>P0001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Fundamental heuristic service-desk</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Electronics</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>464.62</v>
+      </c>
+      <c r="E2" t="n">
+        <v>287</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Thompson PLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>P0002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Automated asymmetric Graphical User Interface</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Books</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>92.79000000000001</v>
+      </c>
+      <c r="E3" t="n">
+        <v>435</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Wilson-Perez</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>P0003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Realigned directional matrix</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Books</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>303.07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>42</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Chaney-Glover</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>P0004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Visionary 6thgeneration throughput</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>230.52</v>
+      </c>
+      <c r="E5" t="n">
+        <v>127</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Adams, Hernandez and Vaughn</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>P0005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Profound real-time secured line</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Electronics</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>388.87</v>
+      </c>
+      <c r="E6" t="n">
+        <v>384</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Mccarthy Group</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>P0006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Persevering web-enabled budgetary management</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Clothing</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>378.83</v>
+      </c>
+      <c r="E7" t="n">
+        <v>106</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Harrington PLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>P0007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Customer-focused next generation analyzer</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>494.17</v>
+      </c>
+      <c r="E8" t="n">
+        <v>185</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garcia, Soto and Pitts</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>P0008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Multi-lateral cohesive superstructure</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>219.23</v>
+      </c>
+      <c r="E9" t="n">
+        <v>316</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Erickson-Gill</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>P0009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Proactive upward-trending attitude</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Clothing</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>333.68</v>
+      </c>
+      <c r="E10" t="n">
+        <v>329</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Holland LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>P0010</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Devolved bottom-line customer loyalty</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>157.98</v>
+      </c>
+      <c r="E11" t="n">
+        <v>45</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Montes-Hammond</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>P0011</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Adaptive dynamic workforce</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>111.73</v>
+      </c>
+      <c r="E12" t="n">
+        <v>271</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Peterson-Wagner</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>P0012</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Configurable encompassing hub</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Books</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>155.91</v>
+      </c>
+      <c r="E13" t="n">
+        <v>115</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Fischer, Ward and Ortega</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>P0013</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Distributed web-enabled system engine</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Electronics</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>261.88</v>
+      </c>
+      <c r="E14" t="n">
+        <v>403</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Fisher, Perez and Pham</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>P0014</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Open-source incremental knowledgebase</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>300.27</v>
+      </c>
+      <c r="E15" t="n">
+        <v>346</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Norton, Cox and Johnson</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>P0015</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Digitized zero administration access</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Books</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>93.02</v>
+      </c>
+      <c r="E16" t="n">
+        <v>136</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Drake, Acevedo and Miller</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>P0016</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Intuitive impactful throughput</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>321.34</v>
+      </c>
+      <c r="E17" t="n">
+        <v>107</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Hamilton Group</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>P0017</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Virtual 5thgeneration protocol</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>430.67</v>
+      </c>
+      <c r="E18" t="n">
+        <v>37</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Hernandez, Andrews and Levine</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>P0018</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Universal stable model</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Electronics</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>208.94</v>
+      </c>
+      <c r="E19" t="n">
+        <v>260</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Barnes-Blackwell</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>P0019</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Total neutral framework</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Books</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>400.47</v>
+      </c>
+      <c r="E20" t="n">
+        <v>113</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Newton, Blankenship and Smith</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>P0020</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Grass-roots multi-tasking pricing structure</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>107.65</v>
+      </c>
+      <c r="E21" t="n">
+        <v>339</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Graves Group</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>P0021</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Stand-alone demand-driven moratorium</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Electronics</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>78.7</v>
+      </c>
+      <c r="E22" t="n">
+        <v>215</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Kramer, Pearson and Terry</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>P0022</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Streamlined impactful time-frame</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>439.29</v>
+      </c>
+      <c r="E23" t="n">
+        <v>342</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Ibarra Inc</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>P0023</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Automated national groupware</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Clothing</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>100.8</v>
+      </c>
+      <c r="E24" t="n">
+        <v>276</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Hardy-Singh</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>P0024</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>De-engineered multi-state moratorium</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Clothing</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>436.6</v>
+      </c>
+      <c r="E25" t="n">
+        <v>381</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Lewis-Hunt</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>P0025</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Integrated multi-state Graphical User Interface</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>175.19</v>
+      </c>
+      <c r="E26" t="n">
+        <v>466</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Moore, Johnson and Hogan</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>P0026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Reverse-engineered empowering encoding</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Books</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>170.4</v>
+      </c>
+      <c r="E27" t="n">
+        <v>441</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Barber-Benitez</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>P0027</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Customizable upward-trending approach</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>100.33</v>
+      </c>
+      <c r="E28" t="n">
+        <v>437</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Green-Romero</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>P0028</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Decentralized actuating system engine</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Clothing</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>197.63</v>
+      </c>
+      <c r="E29" t="n">
+        <v>26</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Pugh, West and Armstrong</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>P0029</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Adaptive logistical Graphical User Interface</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Books</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>415.62</v>
+      </c>
+      <c r="E30" t="n">
+        <v>438</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Trujillo PLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>P0030</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Re-contextualized transitional product</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Books</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>119.04</v>
+      </c>
+      <c r="E31" t="n">
+        <v>227</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Ferguson, Larson and Bell</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>P0031</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Horizontal static toolset</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>64.19</v>
+      </c>
+      <c r="E32" t="n">
+        <v>202</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Armstrong, Taylor and Gray</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>P0032</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>User-centric dynamic benchmark</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Clothing</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>366.19</v>
+      </c>
+      <c r="E33" t="n">
+        <v>141</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Black-Lee</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>P0033</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Vision-oriented high-level knowledgebase</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Clothing</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>320.32</v>
+      </c>
+      <c r="E34" t="n">
+        <v>99</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Thomas Group</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>P0034</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Open-source attitude-oriented array</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>413.68</v>
+      </c>
+      <c r="E35" t="n">
+        <v>45</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Coleman and Sons</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>P0035</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Phased didactic knowledge user</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Books</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>352.93</v>
+      </c>
+      <c r="E36" t="n">
+        <v>5</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Wood PLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>P0036</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Open-architected optimizing open architecture</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Clothing</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>184.82</v>
+      </c>
+      <c r="E37" t="n">
+        <v>198</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Maxwell, Wiggins and Silva</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>P0037</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Sharable interactive intranet</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>159.84</v>
+      </c>
+      <c r="E38" t="n">
+        <v>498</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Galvan, Burns and Mcpherson</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>P0038</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Diverse client-server middleware</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Books</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>293.17</v>
+      </c>
+      <c r="E39" t="n">
+        <v>406</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Washington Group</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>P0039</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>De-engineered tertiary migration</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Books</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>486.34</v>
+      </c>
+      <c r="E40" t="n">
+        <v>184</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Wilson, Lewis and Kennedy</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>P0040</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>User-friendly cohesive open architecture</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>228.34</v>
+      </c>
+      <c r="E41" t="n">
+        <v>305</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Dorsey-Wilson</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>P0041</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Open-source bifurcated capability</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Clothing</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>493.89</v>
+      </c>
+      <c r="E42" t="n">
+        <v>269</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Armstrong-Williams</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>P0042</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Distributed bottom-line hub</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Clothing</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>443.48</v>
+      </c>
+      <c r="E43" t="n">
+        <v>82</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Ritter-Turner</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>P0043</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Pre-emptive 4thgeneration utilization</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>448.46</v>
+      </c>
+      <c r="E44" t="n">
+        <v>152</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Thomas PLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>P0044</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Operative actuating function</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>477.63</v>
+      </c>
+      <c r="E45" t="n">
+        <v>385</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Lewis-Fuentes</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>P0045</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Pre-emptive 24hour capability</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Electronics</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>495.26</v>
+      </c>
+      <c r="E46" t="n">
+        <v>202</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Bailey, Harrell and Butler</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>P0046</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Re-engineered fault-tolerant open system</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>198.24</v>
+      </c>
+      <c r="E47" t="n">
+        <v>12</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Mccullough-Harrington</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>P0047</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Phased uniform portal</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>194.96</v>
+      </c>
+      <c r="E48" t="n">
+        <v>8</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Gill PLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>P0048</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Sharable logistical task-force</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>386.21</v>
+      </c>
+      <c r="E49" t="n">
+        <v>35</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Contreras-Hernandez</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>P0049</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Upgradable fresh-thinking array</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Books</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>141.95</v>
+      </c>
+      <c r="E50" t="n">
+        <v>473</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Beck, Ortiz and Hall</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>P0050</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Object-based global moratorium</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Books</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>369.88</v>
+      </c>
+      <c r="E51" t="n">
+        <v>272</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Rubio Group</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>product_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>unit_price</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>stock_quantity</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>supplier</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>P0001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>User-centric even-keeled project</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>206.55</v>
+      </c>
+      <c r="E2" t="n">
+        <v>159</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Cline Ltd</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>P0002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Assimilated object-oriented product</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Books</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>181.64</v>
+      </c>
+      <c r="E3" t="n">
+        <v>328</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Parker, Brewer and Schneider</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>P0003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Configurable content-based process improvement</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Clothing</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>318.1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>145</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Ray, Brown and Hudson</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>P0004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Ergonomic web-enabled leverage</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>377.63</v>
+      </c>
+      <c r="E5" t="n">
+        <v>207</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Prince, Martinez and Mayer</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>P0005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Enterprise-wide 3rdgeneration focus group</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>169.56</v>
+      </c>
+      <c r="E6" t="n">
+        <v>158</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Sanchez Ltd</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>P0006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Reduced leadingedge artificial intelligence</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Books</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>230.87</v>
+      </c>
+      <c r="E7" t="n">
+        <v>451</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Lawson, Morales and Williams</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>P0007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Ameliorated global Internet solution</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Books</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>423.36</v>
+      </c>
+      <c r="E8" t="n">
+        <v>153</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Perry PLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>P0008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Intuitive homogeneous extranet</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Electronics</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>541.5599999999999</v>
+      </c>
+      <c r="E9" t="n">
+        <v>149</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Wilson Inc</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>P0009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Quality-focused composite forecast</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>332.52</v>
+      </c>
+      <c r="E10" t="n">
+        <v>9</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>White Inc</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>P0010</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Distributed fault-tolerant installation</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>299.6</v>
+      </c>
+      <c r="E11" t="n">
+        <v>305</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Jackson, Mendez and Nguyen</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>P0011</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Assimilated transitional approach</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Clothing</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>235.87</v>
+      </c>
+      <c r="E12" t="n">
+        <v>261</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Price-Flores</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>P0012</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Open-source fresh-thinking firmware</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Clothing</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>224.28</v>
+      </c>
+      <c r="E13" t="n">
+        <v>21</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>David-Lam</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>P0013</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Business-focused dedicated encoding</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>493.55</v>
+      </c>
+      <c r="E14" t="n">
+        <v>420</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Willis, Vasquez and Goodwin</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>P0014</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Networked bifurcated flexibility</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Books</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>182.49</v>
+      </c>
+      <c r="E15" t="n">
+        <v>99</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Flores PLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>P0015</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Open-source asymmetric matrices</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>116.1</v>
+      </c>
+      <c r="E16" t="n">
+        <v>8</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Russell and Sons</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>P0016</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Ameliorated encompassing neural-net</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>134.09</v>
+      </c>
+      <c r="E17" t="n">
+        <v>378</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Leonard, Sanchez and Peters</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>P0017</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>De-engineered exuding open system</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Electronics</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>193.08</v>
+      </c>
+      <c r="E18" t="n">
+        <v>310</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Griffin-Mathis</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>P0018</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Profit-focused demand-driven toolset</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>426.01</v>
+      </c>
+      <c r="E19" t="n">
+        <v>271</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Brooks and Sons</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>P0019</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Fully-configurable national interface</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>109.97</v>
+      </c>
+      <c r="E20" t="n">
+        <v>380</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Hayes, Smith and Marshall</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>P0020</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Secured explicit projection</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Electronics</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>342.76</v>
+      </c>
+      <c r="E21" t="n">
+        <v>461</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Smith Group</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>P0021</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Future-proofed radical extranet</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>194.96</v>
+      </c>
+      <c r="E22" t="n">
+        <v>201</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>James, Bell and Chen</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>P0022</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Reduced multimedia forecast</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Books</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>119.33</v>
+      </c>
+      <c r="E23" t="n">
+        <v>147</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Martin PLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>P0023</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Re-contextualized asymmetric framework</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Clothing</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>287.53</v>
+      </c>
+      <c r="E24" t="n">
+        <v>46</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Foster Inc</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>P0024</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Devolved uniform open architecture</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>81.97</v>
+      </c>
+      <c r="E25" t="n">
+        <v>212</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Johns-Clark</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>P0025</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Profit-focused foreground software</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Books</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>462.49</v>
+      </c>
+      <c r="E26" t="n">
+        <v>131</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Reid-Petty</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>P0026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Triple-buffered local flexibility</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>425.96</v>
+      </c>
+      <c r="E27" t="n">
+        <v>50</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Bates LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>P0027</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Mandatory demand-driven knowledgebase</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Clothing</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>46.27</v>
+      </c>
+      <c r="E28" t="n">
+        <v>201</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Murphy, Sloan and Anderson</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>P0028</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Adaptive real-time leverage</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>230.89</v>
+      </c>
+      <c r="E29" t="n">
+        <v>301</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Valenzuela Ltd</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>P0029</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Enhanced incremental open architecture</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Books</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>96.62</v>
+      </c>
+      <c r="E30" t="n">
+        <v>443</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Warner, Farmer and Medina</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>P0030</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Streamlined solution-oriented archive</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>182.89</v>
+      </c>
+      <c r="E31" t="n">
+        <v>485</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Johnson, Collier and Powers</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>P0031</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Synergistic bottom-line help-desk</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>43.14</v>
+      </c>
+      <c r="E32" t="n">
+        <v>191</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Carey-Howard</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>P0032</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Enhanced zero administration workforce</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>169.6</v>
+      </c>
+      <c r="E33" t="n">
+        <v>488</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Terrell, Martinez and Wood</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>P0033</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Ergonomic leadingedge access</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Clothing</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>279.07</v>
+      </c>
+      <c r="E34" t="n">
+        <v>245</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Paul LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>P0034</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Synergized tertiary help-desk</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Clothing</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>46.14</v>
+      </c>
+      <c r="E35" t="n">
+        <v>284</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Davis PLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>P0035</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Self-enabling exuding workforce</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Electronics</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>571.4400000000001</v>
+      </c>
+      <c r="E36" t="n">
+        <v>57</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Walker, Baird and Coffey</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>P0036</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Automated even-keeled methodology</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Electronics</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>365.7</v>
+      </c>
+      <c r="E37" t="n">
+        <v>479</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Mann, Clark and Gonzalez</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>P0037</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Sharable hybrid budgetary management</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Electronics</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>350.15</v>
+      </c>
+      <c r="E38" t="n">
+        <v>434</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Carroll-Snyder</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>P0038</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Reactive content-based protocol</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>199.98</v>
+      </c>
+      <c r="E39" t="n">
+        <v>146</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Knight, Fleming and Cunningham</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>P0039</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Cloned optimizing capacity</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Books</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>12.65</v>
+      </c>
+      <c r="E40" t="n">
+        <v>195</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Brown, Green and Hudson</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>P0040</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Focused multi-state superstructure</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>227.03</v>
+      </c>
+      <c r="E41" t="n">
+        <v>295</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Lee-Gregory</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>P0041</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Team-oriented systematic monitoring</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>277.36</v>
+      </c>
+      <c r="E42" t="n">
+        <v>191</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>King, Castro and Gibson</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>P0042</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Optimized secondary service-desk</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Electronics</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>188.48</v>
+      </c>
+      <c r="E43" t="n">
+        <v>242</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Williams, Mcmillan and Reynolds</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>P0043</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Open-source even-keeled capability</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>550.08</v>
+      </c>
+      <c r="E44" t="n">
+        <v>270</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Holmes, Simpson and Holmes</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>P0044</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Balanced uniform definition</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Electronics</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>475.61</v>
+      </c>
+      <c r="E45" t="n">
+        <v>498</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Ramirez Group</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>P0045</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Public-key local functionalities</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Electronics</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>25.94</v>
+      </c>
+      <c r="E46" t="n">
+        <v>94</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Myers LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>P0046</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Configurable object-oriented workforce</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Clothing</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>205.37</v>
+      </c>
+      <c r="E47" t="n">
+        <v>166</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Mooney and Sons</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>P0047</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Team-oriented interactive archive</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>390.39</v>
+      </c>
+      <c r="E48" t="n">
+        <v>65</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Gonzalez LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>P0048</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Integrated asymmetric product</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Books</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>156.37</v>
+      </c>
+      <c r="E49" t="n">
+        <v>53</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Davis, Castillo and Morton</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>P0049</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Reverse-engineered responsive groupware</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Clothing</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>36.2</v>
+      </c>
+      <c r="E50" t="n">
+        <v>442</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Wright-Wells</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>P0050</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Mandatory actuating groupware</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Electronics</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>291.45</v>
+      </c>
+      <c r="E51" t="n">
+        <v>425</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Bauer, Harding and Parsons</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>